--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711EBC3D-9967-4529-8B8F-CC3EEA3784BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9836579B1C14920087EF1A14471D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3091DA05-253E-442C-BFD6-2687FDE7394C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 09-09-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 14-09-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9836579B1C14920087EF1A14471D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3091DA05-253E-442C-BFD6-2687FDE7394C}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9836579B1C14920753E76A64671D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{507AE8E0-4107-47FE-962F-F70EA205744D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9836579B1C14920753E76A64671D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{507AE8E0-4107-47FE-962F-F70EA205744D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA7B78E-57F8-4BEF-8F89-AA96110396AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA7B78E-57F8-4BEF-8F89-AA96110396AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D8D9794-CC5B-4321-BF85-1EAA4A6558AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 14-09-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 17-09-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D8D9794-CC5B-4321-BF85-1EAA4A6558AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9682EB94-47FA-4423-BF23-83BB4C982E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9682EB94-47FA-4423-BF23-83BB4C982E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9836579B1C14920E5BE35831A70D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6920D05F-45FA-4E1C-9DFC-D8B3A6B320FD}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 17-09-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 18-09-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9836579B1C14920E5BE35831A70D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6920D05F-45FA-4E1C-9DFC-D8B3A6B320FD}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9836579B1C14920A76EB78B2E71D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE048705-CFB1-4E17-96B9-C6D045D57B13}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 18-09-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 21-09-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9836579B1C14920A76EB78B2E71D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE048705-CFB1-4E17-96B9-C6D045D57B13}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54024838-E338-4930-B909-3E04A68DCA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54024838-E338-4930-B909-3E04A68DCA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F44DB8-E734-46E9-AB2B-AA126B7FBD46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 21-09-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 22-09-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F44DB8-E734-46E9-AB2B-AA126B7FBD46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7093AD8F-3882-4D6B-A068-E55EA2182842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7093AD8F-3882-4D6B-A068-E55EA2182842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6C1CF2-725E-43A9-9208-C7F3633E5CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 22-09-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 23-09-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6C1CF2-725E-43A9-9208-C7F3633E5CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9836579B1C149206E8EB39D1870D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6252D2DB-F35D-4380-9D59-8938D4006565}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9836579B1C149206E8EB39D1870D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6252D2DB-F35D-4380-9D59-8938D4006565}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB936BD7AB2294920344E33B96670D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48F3E060-A14B-4E9C-9DDB-077754FD2ADB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 23-09-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 24-09-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -43,7 +43,7 @@
     <t>MyClinic (PAS) (MultiMed)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB936BD7AB2294920344E33B96670D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48F3E060-A14B-4E9C-9DDB-077754FD2ADB}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB936BD7AB2294920F126F285B270D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09B931DC-1C56-4588-8861-A10D873EE3FB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB936BD7AB2294920F126F285B270D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09B931DC-1C56-4588-8861-A10D873EE3FB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CF5EE1-F14F-41DC-B549-A48FACE232C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 24-09-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 28-09-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CF5EE1-F14F-41DC-B549-A48FACE232C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB936BD7AB22949209B3EF396D271D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B31E61B-9A29-4D6C-A332-887EE4D7FFF1}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 28-09-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 02-10-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7093AD8F-3882-4D6B-A068-E55EA2182842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267ADEA7-1606-4E59-B68C-A973263A03C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 22-09-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 07-10-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -43,7 +43,7 @@
     <t>MyClinic (PAS) (MultiMed)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB936BD7AB22949209B3EF396D271D885F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B31E61B-9A29-4D6C-A332-887EE4D7FFF1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95B3BB3-F624-4FD6-8D38-5241B8E02BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 02-10-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 07-10-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95B3BB3-F624-4FD6-8D38-5241B8E02BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB936BD7AB22949208C2E329F9A70D885F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FC99E79-FA80-43B3-86C8-1C6E0A89D9BC}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 07-10-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 08-10-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB936BD7AB22949208C2E329F9A70D885F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FC99E79-FA80-43B3-86C8-1C6E0A89D9BC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0AA2D2-7EAC-4AA6-A1B7-675769AAB39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 08-10-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 09-10-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0AA2D2-7EAC-4AA6-A1B7-675769AAB39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5713F538-47F4-47F5-B38A-5EDF12FFD3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5713F538-47F4-47F5-B38A-5EDF12FFD3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB936BD7AB2294920813675848A70D885F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F32587E-47FA-401F-8F19-EA199CEEFF1D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 09-10-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 23-10-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
